--- a/data/trans_orig/IP19C04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>66443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73670</t>
+          <t>73551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71421</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79464</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141255</t>
+          <t>141497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152225</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98219</t>
+          <t>98573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106388</t>
+          <t>106539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97476</t>
+          <t>97431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106680</t>
+          <t>106883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>198692</t>
+          <t>199335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210967</t>
+          <t>211304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63491</t>
+          <t>62840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68570</t>
+          <t>68560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66181</t>
+          <t>66066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74296</t>
+          <t>74053</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132221</t>
+          <t>132094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141539</t>
+          <t>141303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84476</t>
+          <t>84397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>93048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>81779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88583</t>
+          <t>88162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169369</t>
+          <t>169170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180142</t>
+          <t>180002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>56580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322378</t>
+          <t>322060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336811</t>
+          <t>337075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>327682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>343266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>653842</t>
+          <t>656081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>676132</t>
+          <t>677061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66180</t>
+          <t>65933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>60699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>70874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>129835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141924</t>
+          <t>141855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99093</t>
+          <t>99665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108101</t>
+          <t>108007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107548</t>
+          <t>107478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113443</t>
+          <t>113464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209587</t>
+          <t>210031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220229</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>62329</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69308</t>
+          <t>70181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77369</t>
+          <t>77382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134266</t>
+          <t>134904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146048</t>
+          <t>146425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>85213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91992</t>
+          <t>92180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87759</t>
+          <t>87422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95006</t>
+          <t>94944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175788</t>
+          <t>175760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185944</t>
+          <t>185695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322577</t>
+          <t>322351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338130</t>
+          <t>338332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336823</t>
+          <t>336429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>350860</t>
+          <t>351708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664959</t>
+          <t>665727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>686534</t>
+          <t>686422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63250</t>
+          <t>63162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>70126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71088</t>
+          <t>70647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137305</t>
+          <t>136531</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144910</t>
+          <t>144671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95147</t>
+          <t>95374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103517</t>
+          <t>103522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105820</t>
+          <t>105738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196132</t>
+          <t>196621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207810</t>
+          <t>208055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>68610</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74458</t>
+          <t>74448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70081</t>
+          <t>69991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76210</t>
+          <t>76207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>141691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149424</t>
+          <t>149850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>97810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106909</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98546</t>
+          <t>98639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105496</t>
+          <t>105431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199549</t>
+          <t>199862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211196</t>
+          <t>210982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336470</t>
+          <t>335545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350131</t>
+          <t>349844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346901</t>
+          <t>347029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359626</t>
+          <t>359390</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687807</t>
+          <t>688081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706474</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60612</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67455</t>
+          <t>67673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80053</t>
+          <t>79608</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84864</t>
+          <t>84876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143423</t>
+          <t>143162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151980</t>
+          <t>151862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100366</t>
+          <t>99782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110793</t>
+          <t>110540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156807</t>
+          <t>157278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165538</t>
+          <t>165727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260356</t>
+          <t>261628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274412</t>
+          <t>274584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96341</t>
+          <t>97115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104711</t>
+          <t>104785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108832</t>
+          <t>109529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118142</t>
+          <t>118298</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210046</t>
+          <t>209679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221465</t>
+          <t>221675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95479</t>
+          <t>95599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100620</t>
+          <t>100612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103213</t>
+          <t>103753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110249</t>
+          <t>110171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202209</t>
+          <t>202185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209894</t>
+          <t>209982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364133</t>
+          <t>364596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>380314</t>
+          <t>379335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460840</t>
+          <t>460582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474552</t>
+          <t>474775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830475</t>
+          <t>830633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>850884</t>
+          <t>851837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10960</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4864</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2122</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8957</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5718</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10993</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76470</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71228</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79359</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70809</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66443</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73551</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>66716</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73708</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76470</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71195</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79493</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141497</t>
+          <t>140898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>151559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8775</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14727</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6882</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3522</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11488</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3477</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11920</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8775</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14200</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>23037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96904</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106833</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103179</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98573</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>106539</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98141</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>106584</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102856</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>97431</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>106883</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199335</t>
+          <t>198655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211304</t>
+          <t>211475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7032</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3761</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11974</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2552</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6368</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6443</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7032</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11803</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -1527,69 +1527,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>70837</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65895</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74108</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>66656</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62840</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>68560</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62765</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>68556</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70837</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66066</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74053</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,97%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>222</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132094</t>
+          <t>131623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141303</t>
+          <t>141459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4094</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6221</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2941</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11592</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11126</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1881</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8264</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85949</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>81738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>88157</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89768</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>84397</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93048</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>84863</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92896</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,52%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>85949</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>81779</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>88162</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169170</t>
+          <t>169446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180002</t>
+          <t>180218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18948</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34357</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13855</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14407</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28733</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34049</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>36483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>57423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>336112</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>327374</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>342783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>330411</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322060</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>337075</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322197</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>336523</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,15%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>336112</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>327682</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>343266</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>656081</t>
+          <t>655238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>677061</t>
+          <t>676178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8434</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4467</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14186</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3707</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7985</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8730</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8434</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4368</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14543</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66808</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61056</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>70775</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70211</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65933</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72553</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65188</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72529</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66808</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>60699</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70874</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129835</t>
+          <t>129672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141855</t>
+          <t>141759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6706</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8109</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4592</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12934</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13619</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1242</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7228</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111437</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>113423</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104490</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99665</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>108007</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98980</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>108456</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111437</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107478</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>113464</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210031</t>
+          <t>209122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>220490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2335</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10486</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7151</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4035</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12168</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12074</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2371</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9572</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74359</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77418</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,24%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67346</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62329</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70462</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62423</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70712</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74359</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70181</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77382</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134904</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146425</t>
+          <t>146308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8340</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3253</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>797</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7764</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7723</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8879</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92420</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87961</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94951</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89724</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>85213</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92180</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>92208</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>92420</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>87422</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94944</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175760</t>
+          <t>175992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185695</t>
+          <t>186013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14563</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28916</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15659</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31640</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15946</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31191</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14294</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29573</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33571</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>345024</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>337086</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>351439</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>472</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>331771</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322351</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>338332</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322800</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>338045</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>345024</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>336429</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>351708</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665727</t>
+          <t>664590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>686422</t>
+          <t>686877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4574</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3116</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7339</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5150</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74371</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71223</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67725</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63162</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70126</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>63502</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70077</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74371</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>70647</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136531</t>
+          <t>136505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144671</t>
+          <t>144901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10754</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6986</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11809</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11952</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5972</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2854</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11305</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102620</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>97838</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>105717</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100197</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>95374</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>103522</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>95231</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>103745</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102620</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>97287</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>105738</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196621</t>
+          <t>196160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208055</t>
+          <t>207872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2785</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6962</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2959</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6978</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6454</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74078</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69901</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75982</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72629</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>68610</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74448</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69134</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74466</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,09%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74078</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69991</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76207</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141691</t>
+          <t>141294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149850</t>
+          <t>149426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4261</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9348</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6119</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11780</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2775</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11743</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8753</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103131</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>98044</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>105846</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>103471</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106731</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97847</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>106815</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>103131</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>98639</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>105431</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199862</t>
+          <t>199856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210982</t>
+          <t>210675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>107392</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>107392</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>107392</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109590</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109590</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109590</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>107392</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>107392</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>107392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22080</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13357</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27656</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13055</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27246</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>21615</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>354199</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>346564</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>359778</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>344020</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>335545</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>349844</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>335955</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>350146</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>354199</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>347029</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>359390</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688081</t>
+          <t>687573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706006</t>
+          <t>706883</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368644</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>363201</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>363201</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>363201</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9179</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,22 +6639,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6404</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79949</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76951</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>65133</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60587</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83479</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79608</t>
+          <t>64170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84876</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>148611</t>
+          <t>149353</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143162</t>
+          <t>143713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151862</t>
+          <t>152574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10348</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6513</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3193</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13951</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>157603</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>151982</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>160462</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>107220</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99782</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110540</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>162447</t>
+          <t>112161</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>157278</t>
+          <t>108164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165727</t>
+          <t>114681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>269667</t>
+          <t>269764</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>261628</t>
+          <t>263154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>274584</t>
+          <t>274076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5368</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9840</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10550</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>107265</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>100598</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>110041</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>101587</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97115</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>104785</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>115095</t>
+          <t>96722</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109529</t>
+          <t>91383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118298</t>
+          <t>99941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>216682</t>
+          <t>203987</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209679</t>
+          <t>197393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221675</t>
+          <t>209116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7811</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5580</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>101844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>97398</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103987</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>99314</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95599</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100612</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>107813</t>
+          <t>100768</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103753</t>
+          <t>97627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110171</t>
+          <t>102084</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>207128</t>
+          <t>202612</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202185</t>
+          <t>197729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209982</t>
+          <t>205465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8914</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>22960</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12298</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27037</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>446662</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>438135</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>452181</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>528</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>373254</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>364596</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>379335</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>468835</t>
+          <t>379054</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460582</t>
+          <t>371260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474775</t>
+          <t>384751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>842088</t>
+          <t>825715</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>830633</t>
+          <t>814420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>851837</t>
+          <t>834633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
